--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.16495</v>
+        <v>16.73064</v>
       </c>
       <c r="D2" t="n">
-        <v>16.5731</v>
+        <v>16.51553</v>
       </c>
       <c r="E2" t="n">
-        <v>16.64206</v>
+        <v>16.53435</v>
       </c>
       <c r="F2" t="n">
-        <v>43.20071</v>
+        <v>42.1273</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05215</v>
+        <v>0.05096</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81029</v>
+        <v>1.82853</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.4695</v>
+        <v>16.91175</v>
       </c>
       <c r="D3" t="n">
-        <v>16.55521</v>
+        <v>16.45945</v>
       </c>
       <c r="E3" t="n">
-        <v>16.60604</v>
+        <v>16.85503</v>
       </c>
       <c r="F3" t="n">
-        <v>41.83389</v>
+        <v>43.0143</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05035</v>
+        <v>0.05105</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82516</v>
+        <v>1.87287</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.65032</v>
+        <v>16.88953</v>
       </c>
       <c r="D4" t="n">
-        <v>16.71429</v>
+        <v>16.61203</v>
       </c>
       <c r="E4" t="n">
-        <v>16.76154</v>
+        <v>16.69256</v>
       </c>
       <c r="F4" t="n">
-        <v>42.64525</v>
+        <v>42.40044</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05156</v>
+        <v>0.05041</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79558</v>
+        <v>1.81848</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.89848</v>
+        <v>16.84902</v>
       </c>
       <c r="D6" t="n">
-        <v>16.13235</v>
+        <v>16.1955</v>
       </c>
       <c r="E6" t="n">
-        <v>16.85585</v>
+        <v>16.25535</v>
       </c>
       <c r="F6" t="n">
-        <v>21.61989</v>
+        <v>21.84779</v>
       </c>
       <c r="G6" t="n">
-        <v>34.23699</v>
+        <v>35.00293</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.88953</v>
+        <v>16.58075</v>
       </c>
       <c r="D7" t="n">
-        <v>15.95064</v>
+        <v>16.16383</v>
       </c>
       <c r="E7" t="n">
-        <v>16.33313</v>
+        <v>16.27514</v>
       </c>
       <c r="F7" t="n">
-        <v>21.72076</v>
+        <v>21.52624</v>
       </c>
       <c r="G7" t="n">
-        <v>34.51496</v>
+        <v>34.29664</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.91302</v>
+        <v>16.8522</v>
       </c>
       <c r="D8" t="n">
-        <v>15.85399</v>
+        <v>16.12697</v>
       </c>
       <c r="E8" t="n">
-        <v>16.46206</v>
+        <v>16.23494</v>
       </c>
       <c r="F8" t="n">
-        <v>22.26518</v>
+        <v>21.78113</v>
       </c>
       <c r="G8" t="n">
-        <v>33.96542</v>
+        <v>34.63486</v>
       </c>
     </row>
   </sheetData>
